--- a/static/excel/KO_model.xlsx
+++ b/static/excel/KO_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Ratios &amp; FCF" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Segments" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="WACC" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="DCF" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Scorecard" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratios &amp; FCF" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segments" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorecard" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7353,11 +7353,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>346134.710528</v>
+        <v>350566.267419</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $80.45</t>
+          <t>FMP marketCap  |  price $81.48</t>
         </is>
       </c>
     </row>
@@ -7439,11 +7439,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0446</v>
+        <v>0.0457</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-13</t>
+          <t>FRED series DGS10  |  latest: 2026-05-21</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0446</v>
+        <v>0.0457</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         </is>
       </c>
       <c r="B19" s="50" t="n">
-        <v>1.108</v>
+        <v>1.107</v>
       </c>
       <c r="C19" s="44">
         <f> unlevered × (1 + (1 − t) × D/E)</f>
@@ -7540,7 +7540,7 @@
         </is>
       </c>
       <c r="B20" s="51" t="n">
-        <v>0.678</v>
+        <v>0.677</v>
       </c>
       <c r="C20" s="49" t="inlineStr">
         <is>
@@ -7714,11 +7714,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.0542</v>
+        <v>0.0553</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.46% + spread 0.96%</t>
+          <t>Rf 4.57% + spread 0.96%</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="B37" s="48" t="n">
-        <v>0.0454</v>
+        <v>0.046</v>
       </c>
       <c r="C37" s="49" t="inlineStr">
         <is>
@@ -7809,16 +7809,16 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="54" t="inlineStr">
         <is>
-          <t>WACC  =  (E/V × Re)  +  (D/V × Rd × (1 − t))</t>
+          <t>WACC  =  MAX(8.5%, (E/V × Re) + (D/V × Rd × (1 − t)))</t>
         </is>
       </c>
       <c r="B44" s="55">
-        <f>B8*B28+B9*B37*(1-B41)</f>
+        <f>MAX(0.085, B8*B28+B9*B37*(1-B41))</f>
         <v/>
       </c>
       <c r="C44" s="56" t="inlineStr">
         <is>
-          <t>Used as discount rate in DCF tab</t>
+          <t>Floored 8.5% (D-001); raw formula below</t>
         </is>
       </c>
     </row>
@@ -8565,12 +8565,12 @@
       </c>
       <c r="G16" s="82" t="inlineStr">
         <is>
-          <t>48,726 — 49,625</t>
+          <t>48,518 — 50,569</t>
         </is>
       </c>
       <c r="H16" s="82" t="inlineStr">
         <is>
-          <t>48,668 — 52,466</t>
+          <t>48,552 — 53,232</t>
         </is>
       </c>
       <c r="I16" s="82" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="J16" s="82" t="inlineStr">
         <is>
-          <t>52,791 — 56,062</t>
+          <t>52,703 — 56,526</t>
         </is>
       </c>
       <c r="K16" s="82" t="inlineStr">
         <is>
-          <t>55,869 — 59,330</t>
+          <t>55,776 — 59,821</t>
         </is>
       </c>
       <c r="L16" s="83" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="G21" s="82" t="inlineStr">
         <is>
-          <t>17,436 — 17,758</t>
+          <t>17,361 — 18,095</t>
         </is>
       </c>
       <c r="H21" s="82" t="inlineStr">
         <is>
-          <t>17,415 — 18,774</t>
+          <t>17,373 — 19,048</t>
         </is>
       </c>
       <c r="I21" s="82" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="J21" s="82" t="inlineStr">
         <is>
-          <t>18,890 — 20,061</t>
+          <t>18,859 — 20,227</t>
         </is>
       </c>
       <c r="K21" s="82" t="inlineStr">
         <is>
-          <t>19,992 — 21,230</t>
+          <t>19,959 — 21,406</t>
         </is>
       </c>
       <c r="L21" s="83" t="inlineStr">
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="B38" s="101" t="n">
-        <v>10</v>
+        <v>15.4</v>
       </c>
       <c r="C38" s="99" t="n"/>
       <c r="D38" s="99" t="n"/>
@@ -9461,7 +9461,7 @@
       <c r="L38" s="99" t="n"/>
       <c r="M38" s="74" t="inlineStr">
         <is>
-          <t>Growth tier: LOW (3.7% 3yr avg rev growth).  Bear 8x / Base 10x / Bull 12x.  Override manually if needed.</t>
+          <t>Growth tier: LOW (3.7% 3yr avg rev growth).  Bear 12x / Base 15x / Bull 18x.  Override manually if needed.</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="B61" s="112" t="n">
-        <v>80.45</v>
+        <v>81.48</v>
       </c>
       <c r="C61" s="104" t="n"/>
       <c r="D61" s="104" t="n"/>
@@ -10063,7 +10063,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="114" t="inlineStr">
         <is>
-          <t>JS SCORECARD — KO  |  Master Prompt v2  |  15 May 2026  |  Sector bucket: Stable Compounder</t>
+          <t>JS SCORECARD — KO  |  Master Prompt v2  |  25 May 2026  |  Sector bucket: Stable Compounder</t>
         </is>
       </c>
     </row>
@@ -10196,7 +10196,7 @@
       </c>
       <c r="D9" s="130" t="inlineStr">
         <is>
-          <t>GM 61.6% ✓ (&gt;40%)  |  GM trend +3.5% ✓ (&gt;+1pp)  |  ROIC-WACC +13.8% ✓ (&gt;+5pp)  |  Rev consistency σ=3.7% ✓ (&lt;8%)  [4/4 indicators positive — proxy score]</t>
+          <t>GM 61.6% ✓ (&gt;40%)  |  GM trend +3.5% ✓ (&gt;+1pp)  |  ROIC-WACC +11.2% ✓ (&gt;+5pp)  |  Rev consistency σ=3.7% ✓ (&lt;8%)  [4/4 indicators positive — proxy score]</t>
         </is>
       </c>
       <c r="E9" s="131" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="H9" s="134" t="inlineStr">
         <is>
-          <t>GM 61.6% ✓ (&gt;40%)  |  GM trend +3.5% ✓ (&gt;+1pp)  |  ROIC-WACC +13.8% ✓ (&gt;+5pp)  |  Rev consistency σ=3.7% ✓ (&lt;8%)  [4/4 indicators positive — proxy score]</t>
+          <t>GM 61.6% ✓ (&gt;40%)  |  GM trend +3.5% ✓ (&gt;+1pp)  |  ROIC-WACC +11.2% ✓ (&gt;+5pp)  |  Rev consistency σ=3.7% ✓ (&lt;8%)  [4/4 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="D11" s="130" t="inlineStr">
         <is>
-          <t>ROIC trend +0.2% ✓ (≥-2pp)  |  GM maintained +3.5% ✓  |  Op margin +3.3% ✓ (≥-2pp)  |  Capital returns HIGH ✓  |  Share count -0.1%/yr ✓ (net buyback)  |  Goodwill/Equity 48% ✗ (&lt;40%)  [5/6 indicators positive — proxy score]</t>
+          <t>ROIC trend +0.2% ✓ (&gt;=-2pp)  |  GM maintained +3.5% ✓  |  Op margin +3.3% ✓ (≥-2pp)  |  Capital returns HIGH ✓  |  Share count -0.1%/yr ✓ (net buyback)  |  Goodwill/Equity 48% ✗ (&lt;40%)  [5/6 indicators positive — proxy score]</t>
         </is>
       </c>
       <c r="E11" s="135" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="H11" s="134" t="inlineStr">
         <is>
-          <t>ROIC trend +0.2% ✓ (≥-2pp)  |  GM maintained +3.5% ✓  |  Op margin +3.3% ✓ (≥-2pp)  |  Capital returns HIGH ✓  |  Share count -0.1%/yr ✓ (net buyback)  |  Goodwill/Equity 48% ✗ (&lt;40%)  [5/6 indicators positive — proxy score]</t>
+          <t>ROIC trend +0.2% ✓ (&gt;=-2pp)  |  GM maintained +3.5% ✓  |  Op margin +3.3% ✓ (≥-2pp)  |  Capital returns HIGH ✓  |  Share count -0.1%/yr ✓ (net buyback)  |  Goodwill/Equity 48% ✗ (&lt;40%)  [5/6 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="D20" s="130" t="inlineStr">
         <is>
-          <t>Rev growth σ=3.7%  |  Op margin σ=2.5%  [proxy — lower σ = lower risk = higher score]</t>
+          <t>Rev growth σ=3.7%  |  OM trend +2.0%, σ=2.5%  [quality = direction + stability]</t>
         </is>
       </c>
       <c r="E20" s="135" t="inlineStr">
@@ -10545,7 +10545,7 @@
         </is>
       </c>
       <c r="F20" s="132" t="n">
-        <v>8.33</v>
+        <v>6.67</v>
       </c>
       <c r="G20" s="133">
         <f>IF(F20="",0,C20*F20*10)</f>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H20" s="134" t="inlineStr">
         <is>
-          <t>Rev growth σ=3.7%  |  Op margin σ=2.5%  [proxy — lower σ = lower risk = higher score]</t>
+          <t>Rev growth σ=3.7%  |  OM trend +2.0%, σ=2.5%  [quality = direction + stability]</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="D22" s="130" t="inlineStr">
         <is>
-          <t>Current 23.0x  |  5yr avg 25.4x  |  DCF-implied 21.3x  [+8% vs benchmark]</t>
+          <t>Current 23.0x  |  5yr avg 25.4x  |  DCF-implied 15.3x [ref only — not used as benchmark]  [-9% vs benchmark]  [trail=8.42 | fwd_pe=24.9x→7.30 | abs=7.0 → blended 40/40/20=7.68]  PEG=339.89 (fwd_pe=24.9x / eps_growth=7%)  [revision:Modest upgrade expected→+0.25]</t>
         </is>
       </c>
       <c r="E22" s="135" t="inlineStr">
@@ -10589,7 +10589,7 @@
         </is>
       </c>
       <c r="F22" s="132" t="n">
-        <v>5.72</v>
+        <v>7.93</v>
       </c>
       <c r="G22" s="133">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="H22" s="134" t="inlineStr">
         <is>
-          <t>Current 23.0x  |  5yr avg 25.4x  |  DCF-implied 21.3x  [+8% vs benchmark]</t>
+          <t>Current 23.0x  |  5yr avg 25.4x  |  DCF-implied 15.3x [ref only — not used as benchmark]  [-9% vs benchmark]  [trail=8.42 | fwd_pe=24.9x→7.30 | abs=7.0 → blended 40/40/20=7.68]  PEG=339.89 (fwd_pe=24.9x / eps_growth=7%)  [revision:Modest upgrade expected→+0.25]</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="D23" s="130" t="inlineStr">
         <is>
-          <t>Current 56.8x  |  5yr avg 38.2x  |  DCF-implied 52.8x  [+49% vs benchmark]</t>
+          <t>Current 56.8x  |  5yr avg 38.2x  |  DCF-implied 37.9x [ref only — not used as benchmark]  [+49% vs benchmark]  [trail=0.16 | fwd_pfcf=64.6x→0.00 | abs=0.0 → blended 40/40/20=0.06]  [fcf_yield=1.8% vs rf=4.6%  spread=-2.8%→modifier=-0.50]</t>
         </is>
       </c>
       <c r="E23" s="137" t="inlineStr">
@@ -10626,7 +10626,7 @@
         </is>
       </c>
       <c r="F23" s="132" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="G23" s="133">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="H23" s="134" t="inlineStr">
         <is>
-          <t>Current 56.8x  |  5yr avg 38.2x  |  DCF-implied 52.8x  [+49% vs benchmark]</t>
+          <t>Current 56.8x  |  5yr avg 38.2x  |  DCF-implied 37.9x [ref only — not used as benchmark]  [+49% vs benchmark]  [trail=0.16 | fwd_pfcf=64.6x→0.00 | abs=0.0 → blended 40/40/20=0.06]  [fcf_yield=1.8% vs rf=4.6%  spread=-2.8%→modifier=-0.50]</t>
         </is>
       </c>
     </row>

--- a/static/excel/KO_model.xlsx
+++ b/static/excel/KO_model.xlsx
@@ -7439,11 +7439,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0457</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-21</t>
+          <t>FRED series DGS10  |  latest: 2026-05-22</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0457</v>
+        <v>0.0456</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7653,25 +7653,27 @@
       </c>
       <c r="B31" s="53" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C31" s="44" t="inlineStr">
         <is>
-          <t>FMP /ratings endpoint</t>
+          <t>User input</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>FRED matched yield</t>
-        </is>
-      </c>
-      <c r="B32" s="53" t="n"/>
+          <t>FRED matched yield  (rating-tier index)</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="n">
+        <v>0.0507</v>
+      </c>
       <c r="C32" s="44" t="inlineStr">
         <is>
-          <t>No rating returned — FRED method not applicable</t>
+          <t>FRED BAMLC0A3CAEY — A</t>
         </is>
       </c>
     </row>
@@ -7714,11 +7716,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.0553</v>
+        <v>0.05519999999999999</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.57% + spread 0.96%</t>
+          <t>Rf 4.56% + spread 0.96%</t>
         </is>
       </c>
     </row>
@@ -7744,11 +7746,11 @@
         </is>
       </c>
       <c r="B37" s="48" t="n">
-        <v>0.046</v>
+        <v>0.0475</v>
       </c>
       <c r="C37" s="49" t="inlineStr">
         <is>
-          <t>Default = average of 2 source(s) above — override freely</t>
+          <t>Default = average of 3 source(s) above — override freely</t>
         </is>
       </c>
     </row>
@@ -10063,7 +10065,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="114" t="inlineStr">
         <is>
-          <t>JS SCORECARD — KO  |  Master Prompt v2  |  25 May 2026  |  Sector bucket: Stable Compounder</t>
+          <t>JS SCORECARD — KO  |  Master Prompt v2  |  27 May 2026  |  Sector bucket: Stable Compounder</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10582,7 @@
       </c>
       <c r="D22" s="130" t="inlineStr">
         <is>
-          <t>Current 23.0x  |  5yr avg 25.4x  |  DCF-implied 15.3x [ref only — not used as benchmark]  [-9% vs benchmark]  [trail=8.42 | fwd_pe=24.9x→7.30 | abs=7.0 → blended 40/40/20=7.68]  PEG=339.89 (fwd_pe=24.9x / eps_growth=7%)  [revision:Modest upgrade expected→+0.25]</t>
+          <t>Fwd P/E 24.9x (scoring basis)  |  5yr avg 24.9x  |  DCF-implied 15.3x [ref only — not used as benchmark]  [+0% vs benchmark]  [trail=7.00 | fwd_pe=24.9x→7.00 | abs=7.0 → blended 40/40/20=7.00]  PEG=339.89 (fwd_pe=24.9x / eps_growth=7%)  [revision:Modest upgrade expected→+0.25]</t>
         </is>
       </c>
       <c r="E22" s="135" t="inlineStr">
@@ -10589,7 +10591,7 @@
         </is>
       </c>
       <c r="F22" s="132" t="n">
-        <v>7.93</v>
+        <v>7.25</v>
       </c>
       <c r="G22" s="133">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10597,7 +10599,7 @@
       </c>
       <c r="H22" s="134" t="inlineStr">
         <is>
-          <t>Current 23.0x  |  5yr avg 25.4x  |  DCF-implied 15.3x [ref only — not used as benchmark]  [-9% vs benchmark]  [trail=8.42 | fwd_pe=24.9x→7.30 | abs=7.0 → blended 40/40/20=7.68]  PEG=339.89 (fwd_pe=24.9x / eps_growth=7%)  [revision:Modest upgrade expected→+0.25]</t>
+          <t>Fwd P/E 24.9x (scoring basis)  |  5yr avg 24.9x  |  DCF-implied 15.3x [ref only — not used as benchmark]  [+0% vs benchmark]  [trail=7.00 | fwd_pe=24.9x→7.00 | abs=7.0 → blended 40/40/20=7.00]  PEG=339.89 (fwd_pe=24.9x / eps_growth=7%)  [revision:Modest upgrade expected→+0.25]</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10619,7 @@
       </c>
       <c r="D23" s="130" t="inlineStr">
         <is>
-          <t>Current 56.8x  |  5yr avg 38.2x  |  DCF-implied 37.9x [ref only — not used as benchmark]  [+49% vs benchmark]  [trail=0.16 | fwd_pfcf=64.6x→0.00 | abs=0.0 → blended 40/40/20=0.06]  [fcf_yield=1.8% vs rf=4.6%  spread=-2.8%→modifier=-0.50]</t>
+          <t>Current 56.8x  |  5yr avg 41.9x  |  DCF-implied 37.9x [ref only — not used as benchmark]  [+36% vs benchmark]  [trail=1.73 | fwd_pfcf=64.6x→0.00 | abs=0.0 → blended 40/40/20=0.69]  [fcf_yield=1.8% vs rf=4.6%  spread=-2.8%→modifier=-0.50]</t>
         </is>
       </c>
       <c r="E23" s="137" t="inlineStr">
@@ -10626,7 +10628,7 @@
         </is>
       </c>
       <c r="F23" s="132" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="G23" s="133">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10634,7 +10636,7 @@
       </c>
       <c r="H23" s="134" t="inlineStr">
         <is>
-          <t>Current 56.8x  |  5yr avg 38.2x  |  DCF-implied 37.9x [ref only — not used as benchmark]  [+49% vs benchmark]  [trail=0.16 | fwd_pfcf=64.6x→0.00 | abs=0.0 → blended 40/40/20=0.06]  [fcf_yield=1.8% vs rf=4.6%  spread=-2.8%→modifier=-0.50]</t>
+          <t>Current 56.8x  |  5yr avg 41.9x  |  DCF-implied 37.9x [ref only — not used as benchmark]  [+36% vs benchmark]  [trail=1.73 | fwd_pfcf=64.6x→0.00 | abs=0.0 → blended 40/40/20=0.69]  [fcf_yield=1.8% vs rf=4.6%  spread=-2.8%→modifier=-0.50]</t>
         </is>
       </c>
     </row>
